--- a/sheets/조재수대금교본/검수/그녀의 웃음 소리 뿐.xlsx
+++ b/sheets/조재수대금교본/검수/그녀의 웃음 소리 뿐.xlsx
@@ -3335,16 +3335,11 @@
     </row>
     <row r="5" ht="91.25" customHeight="true">
       <c r="A5" s="0"/>
-      <c r="B5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B5" s="21"/>
       <c r="C5" s="23"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">應
-‹</t>
+          <t xml:space="preserve">應</t>
         </is>
       </c>
       <c r="E5" s="23"/>
@@ -3357,8 +3352,7 @@
       <c r="G5" s="23"/>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">應
-‹</t>
+          <t xml:space="preserve">應</t>
         </is>
       </c>
       <c r="I5" s="23"/>
@@ -3396,8 +3390,7 @@
       <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-應
-‹</t>
+應</t>
         </is>
       </c>
       <c r="G6" s="24"/>
@@ -3487,19 +3480,11 @@
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="23"/>
-      <c r="D9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D9" s="21"/>
       <c r="E9" s="23"/>
       <c r="F9" s="21"/>
       <c r="G9" s="23"/>
-      <c r="H9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H9" s="21"/>
       <c r="I9" s="23"/>
       <c r="J9" s="21" t="inlineStr">
         <is>
@@ -3625,7 +3610,7 @@
       <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-太ㄴ</t>
+太</t>
         </is>
       </c>
       <c r="K12" s="23"/>
@@ -3648,8 +3633,7 @@
       <c r="C13" s="23"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋
-‹</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="E13" s="23"/>
@@ -3662,8 +3646,7 @@
       <c r="G13" s="23"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋
-‹</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="I13" s="23"/>
@@ -3710,7 +3693,7 @@
       <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△
-太太ㄴ</t>
+太太</t>
         </is>
       </c>
       <c r="K14" s="24"/>

--- a/sheets/조재수대금교본/검수/그녀의 웃음 소리 뿐.xlsx
+++ b/sheets/조재수대금교본/검수/그녀의 웃음 소리 뿐.xlsx
@@ -3610,7 +3610,7 @@
       <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-太</t>
+太ㄴ</t>
         </is>
       </c>
       <c r="K12" s="23"/>
@@ -3693,7 +3693,7 @@
       <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△
-太太</t>
+太太ㄴ</t>
         </is>
       </c>
       <c r="K14" s="24"/>

--- a/sheets/조재수대금교본/검수/그녀의 웃음 소리 뿐.xlsx
+++ b/sheets/조재수대금교본/검수/그녀의 웃음 소리 뿐.xlsx
@@ -3215,24 +3215,24 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="15.29" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="15.29" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="15.29" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="15.29" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="15.29" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="15.29" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="81.63" customHeight="true">
+    <row r="2" ht="61.54" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" ht="91.25" customHeight="true">
+    <row r="3" ht="68.7" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
       </c>
       <c r="M3" s="22"/>
     </row>
-    <row r="4" ht="91.25" customHeight="true">
+    <row r="4" ht="68.7" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="23"/>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="M4" s="23"/>
     </row>
-    <row r="5" ht="91.25" customHeight="true">
+    <row r="5" ht="68.7" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="23"/>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="M5" s="23"/>
     </row>
-    <row r="6" ht="91.25" customHeight="true">
+    <row r="6" ht="68.7" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
       <c r="L6" s="21"/>
       <c r="M6" s="24"/>
     </row>
-    <row r="7" ht="91.25" customHeight="true">
+    <row r="7" ht="68.7" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="M7" s="22"/>
     </row>
-    <row r="8" ht="91.25" customHeight="true">
+    <row r="8" ht="68.7" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="23"/>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="M8" s="23"/>
     </row>
-    <row r="9" ht="91.25" customHeight="true">
+    <row r="9" ht="68.7" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="23"/>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="M9" s="23"/>
     </row>
-    <row r="10" ht="91.25" customHeight="true">
+    <row r="10" ht="68.7" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
       <c r="L10" s="21"/>
       <c r="M10" s="24"/>
     </row>
-    <row r="11" ht="91.25" customHeight="true">
+    <row r="11" ht="68.7" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="M11" s="22"/>
     </row>
-    <row r="12" ht="91.25" customHeight="true">
+    <row r="12" ht="68.7" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="M12" s="23"/>
     </row>
-    <row r="13" ht="91.25" customHeight="true">
+    <row r="13" ht="68.7" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="M13" s="23"/>
     </row>
-    <row r="14" ht="91.25" customHeight="true">
+    <row r="14" ht="68.7" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="M14" s="24"/>
     </row>
-    <row r="15" ht="91.25" customHeight="true">
+    <row r="15" ht="68.7" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="M15" s="22"/>
     </row>
-    <row r="16" ht="91.25" customHeight="true">
+    <row r="16" ht="68.7" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="23"/>
@@ -3765,7 +3765,7 @@
       </c>
       <c r="M16" s="23"/>
     </row>
-    <row r="17" ht="91.25" customHeight="true">
+    <row r="17" ht="68.7" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="23"/>
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M17" s="23"/>
     </row>
-    <row r="18" ht="91.25" customHeight="true">
+    <row r="18" ht="68.7" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -3834,6 +3834,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="49"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="65"/>
 </worksheet>
 </file>